--- a/out/Attention-Mamba1_metrics.xlsx
+++ b/out/Attention-Mamba1_metrics.xlsx
@@ -472,13 +472,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.001083826110698283</v>
+        <v>0.001083826133981347</v>
       </c>
       <c r="B2" t="n">
         <v>0.03292063623666763</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0233632680028677</v>
+        <v>0.02336326986551285</v>
       </c>
       <c r="D2" t="n">
         <v>0.01643276214599609</v>
